--- a/Documentación/Casos de Uso/RESUMEN Estado de Avance Casos de Uso.xlsx
+++ b/Documentación/Casos de Uso/RESUMEN Estado de Avance Casos de Uso.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moon\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD3F0E7-092B-481D-95AC-78C2BB4E6CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="RESUMEN" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="RESUMEN 2." sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="RESUMEN 3" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="RESUMEN 4" sheetId="4" r:id="rId7"/>
+    <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
+    <sheet name="RESUMEN 2." sheetId="2" r:id="rId2"/>
+    <sheet name="RESUMEN 3" sheetId="3" r:id="rId3"/>
+    <sheet name="RESUMEN 4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="QbH8s92U94r7QLWZIEx7vaYUubUGK9eg21WgE3K1A0g="/>
@@ -19,46 +28,78 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B6">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAAB5Dn_sK8
     (2026-04-28 19:24:12)
 Número que posee el caso de uso dentro del enunciado entregado</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="F6">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAB5Dn_sKU
+    (2026-04-28 19:24:12)
+¿Qué acto(res) forman parte del caso de uso?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAB5Dn_sKs
+    (2026-04-28 19:24:12)
+De los integrantes del equipo ¿Quien es el encargado del desarrollo de este caso de uso?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAAB5Dn_sKo
 Porcentaje de avance    (2026-04-28 19:24:12)
 en donde 0% nada y 100% finalizado</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="E6">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB5Dn_sKs
-    (2026-04-28 19:24:12)
-De los integrantes del equipo ¿Quien es el encargado del desarrollo de este caso de uso?</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="D6">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB5Dn_sKU
-    (2026-04-28 19:24:12)
-¿Qué acto(res) forman parte del caso de uso?</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjZV0JGSv3C5KgF0QnycqhajePZcw=="/>
     </ext>
   </extLst>
@@ -66,46 +107,78 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="D5">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAB5Dn_re4
+    (2026-04-28 19:24:11)
+Número que posee el caso de uso dentro del enunciado entregado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAAB5Dn_sKw
     (2026-04-28 19:24:12)
 ¿Qué acto(res) forman parte del caso de uso?</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="F5">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAB5Dn_sKQ
+    (2026-04-28 19:24:12)
+De los integrantes del equipo ¿Quien es el encargado del desarrollo de este caso de uso?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAAB5Dn_sKg
 Porcentaje de avance    (2026-04-28 19:24:12)
 en donde 0% nada y 100% finalizado</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="E5">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB5Dn_sKQ
-    (2026-04-28 19:24:12)
-De los integrantes del equipo ¿Quien es el encargado del desarrollo de este caso de uso?</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B5">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB5Dn_re4
-    (2026-04-28 19:24:11)
-Número que posee el caso de uso dentro del enunciado entregado</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjD18HESD53CJTPeIOat+pk4vBi9g=="/>
     </ext>
   </extLst>
@@ -113,46 +186,78 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="F5">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAB5Dn_sKI
+    (2026-04-28 19:24:12)
+Número que posee el caso de uso dentro del enunciado entregado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAB5Dn_sKY
+    (2026-04-28 19:24:12)
+¿Qué acto(res) forman parte del caso de uso?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAB5Dn_sKM
+    (2026-04-28 19:24:12)
+De los integrantes del equipo ¿Quien es el encargado del desarrollo de este caso de uso?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAAB5Dn_sLA
 Porcentaje de avance    (2026-04-28 19:24:12)
 en donde 0% nada y 100% finalizado</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="D5">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB5Dn_sKY
-    (2026-04-28 19:24:12)
-¿Qué acto(res) forman parte del caso de uso?</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="E5">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB5Dn_sKM
-    (2026-04-28 19:24:12)
-De los integrantes del equipo ¿Quien es el encargado del desarrollo de este caso de uso?</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B5">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB5Dn_sKI
-    (2026-04-28 19:24:12)
-Número que posee el caso de uso dentro del enunciado entregado</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhenfZCvpjueYJOqHi2yWgXDo6dfw=="/>
     </ext>
   </extLst>
@@ -160,7 +265,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="94">
   <si>
     <t>Problema asignado:</t>
   </si>
@@ -428,72 +533,97 @@
   <si>
     <t>Se graban todos los datos de la Obra en la base de datos. Si el formulario esta incompleto el sistema muestra mensajes de errores (exceptions). Se realiza plan de prueba.</t>
   </si>
+  <si>
+    <t>Gabriel Miranda</t>
+  </si>
+  <si>
+    <t>Falta agregar funciones para calculo de costo y visualización de fotos por observación.</t>
+  </si>
+  <si>
+    <t>Vista de gestión de tickets creada. Se logra cambiar el estado de observaciones en cada ticket</t>
+  </si>
+  <si>
+    <t>Se visualizan tickets y observaciones en pantallas Administrador y Usuario.</t>
+  </si>
+  <si>
+    <t>Creación de tickets completa con datos registrados directamente a la base de datos.</t>
+  </si>
+  <si>
+    <t>Se logra filtrar tickets por estado y a través de barra de búsqueda.</t>
+  </si>
+  <si>
+    <t>Falta desarrollo para implementar fotos.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="12">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF0070C0"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF2E75B5"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -504,7 +634,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -538,12 +668,19 @@
     </fill>
   </fills>
   <borders count="20">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -556,6 +693,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -566,6 +704,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -578,6 +717,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -588,23 +728,30 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -612,27 +759,34 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -642,6 +796,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -656,6 +811,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -668,6 +824,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -682,6 +839,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -696,6 +854,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -708,6 +867,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -722,6 +882,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -730,170 +891,141 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="44">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="17" fillId="4" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="17" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="17" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="4" fontId="9" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="9" fontId="9" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="9" fontId="9" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="9" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="19" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="5" fontId="9" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="9" fontId="9" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="17" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="17" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="6" fontId="9" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="6" fontId="9" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1083,28 +1215,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z220"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.86"/>
-    <col customWidth="1" min="2" max="2" width="9.86"/>
-    <col customWidth="1" min="3" max="3" width="27.57"/>
-    <col customWidth="1" min="4" max="4" width="16.14"/>
-    <col customWidth="1" min="5" max="5" width="39.86"/>
-    <col customWidth="1" min="6" max="6" width="28.29"/>
-    <col customWidth="1" min="7" max="7" width="43.71"/>
-    <col customWidth="1" min="8" max="8" width="42.43"/>
-    <col customWidth="1" min="9" max="26" width="10.71"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="39.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" customWidth="1"/>
+    <col min="7" max="7" width="43.7109375" customWidth="1"/>
+    <col min="8" max="8" width="42.42578125" customWidth="1"/>
+    <col min="9" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1132,7 +1264,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1162,16 +1294,16 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1194,14 +1326,14 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="1:26" ht="15" customHeight="1">
+      <c r="A4" s="6"/>
+      <c r="B4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1224,14 +1356,14 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:26" ht="15" customHeight="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1254,29 +1386,29 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:26" ht="31.5">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="11" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="1"/>
@@ -1298,29 +1430,29 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:26" ht="25.5">
+      <c r="A7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="14" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="1"/>
@@ -1342,29 +1474,29 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="21">
-        <v>46143.0</v>
-      </c>
-      <c r="B8" s="22" t="s">
+    <row r="8" spans="1:26" ht="38.25">
+      <c r="A8" s="15">
+        <v>46143</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="19">
         <v>0.9</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I8" s="1"/>
@@ -1378,33 +1510,33 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21">
-        <v>46144.0</v>
-      </c>
-      <c r="B9" s="22" t="s">
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+    </row>
+    <row r="9" spans="1:26" ht="25.5">
+      <c r="A9" s="15">
+        <v>46144</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="19">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1416,37 +1548,37 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="21">
-        <v>46145.0</v>
-      </c>
-      <c r="B10" s="30" t="s">
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+    </row>
+    <row r="10" spans="1:26" ht="38.25">
+      <c r="A10" s="15">
+        <v>46145</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="19">
         <v>0.2</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="26"/>
+      <c r="H10" s="18"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1458,37 +1590,37 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="21">
-        <v>46146.0</v>
-      </c>
-      <c r="B11" s="30" t="s">
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+    </row>
+    <row r="11" spans="1:26" ht="38.25">
+      <c r="A11" s="15">
+        <v>46146</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="19">
         <v>0.2</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="26"/>
+      <c r="H11" s="18"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1500,36 +1632,38 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="27"/>
-      <c r="Y11" s="27"/>
-      <c r="Z11" s="27"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="21">
-        <v>46147.0</v>
-      </c>
-      <c r="B12" s="32" t="s">
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+    </row>
+    <row r="12" spans="1:26" ht="25.5">
+      <c r="A12" s="15">
+        <v>46147</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="35" t="s">
+      <c r="E12" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="37"/>
+      <c r="I12" s="27"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1540,34 +1674,34 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21">
-        <v>46148.0</v>
-      </c>
-      <c r="B13" s="32" t="s">
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="15">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="37"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="26">
+        <v>0</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="27"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1578,36 +1712,36 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="21">
-        <v>46149.0</v>
-      </c>
-      <c r="B14" s="32" t="s">
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="28"/>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" s="15">
+        <v>46149</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="26">
         <v>0.1</v>
       </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="37"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="27"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1618,82 +1752,82 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="38"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21">
-        <v>46145.0</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="28"/>
+    </row>
+    <row r="15" spans="1:26" ht="38.25">
+      <c r="A15" s="15">
+        <v>46145</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="39">
+      <c r="E15" s="30"/>
+      <c r="F15" s="26">
         <v>0.9</v>
       </c>
-      <c r="G15" s="34" t="s">
+      <c r="G15" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="34" t="s">
+      <c r="H15" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="44"/>
-      <c r="V15" s="44"/>
-      <c r="W15" s="44"/>
-      <c r="X15" s="44"/>
-      <c r="Y15" s="44"/>
-      <c r="Z15" s="44"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="21">
-        <v>46145.0</v>
-      </c>
-      <c r="B16" s="45" t="s">
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+    </row>
+    <row r="16" spans="1:26" ht="76.5">
+      <c r="A16" s="15">
+        <v>46145</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="E16" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="36">
         <v>0.7</v>
       </c>
-      <c r="G16" s="47" t="s">
+      <c r="G16" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="H16" s="47" t="s">
+      <c r="H16" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="37"/>
+      <c r="I16" s="27"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1704,40 +1838,40 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="49"/>
-      <c r="U16" s="49"/>
-      <c r="V16" s="49"/>
-      <c r="W16" s="49"/>
-      <c r="X16" s="49"/>
-      <c r="Y16" s="49"/>
-      <c r="Z16" s="49"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21">
-        <v>46145.0</v>
-      </c>
-      <c r="B17" s="45" t="s">
+      <c r="T16" s="37"/>
+      <c r="U16" s="37"/>
+      <c r="V16" s="37"/>
+      <c r="W16" s="37"/>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="37"/>
+      <c r="Z16" s="37"/>
+    </row>
+    <row r="17" spans="1:26" ht="25.5">
+      <c r="A17" s="15">
+        <v>46145</v>
+      </c>
+      <c r="B17" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="36">
         <v>0.7</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G17" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="H17" s="47" t="s">
+      <c r="H17" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="37"/>
+      <c r="I17" s="27"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1748,34 +1882,34 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="49"/>
-      <c r="W17" s="49"/>
-      <c r="X17" s="49"/>
-      <c r="Y17" s="49"/>
-      <c r="Z17" s="49"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="21">
-        <v>46153.0</v>
-      </c>
-      <c r="B18" s="45" t="s">
+      <c r="T17" s="37"/>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="37"/>
+      <c r="X17" s="37"/>
+      <c r="Y17" s="37"/>
+      <c r="Z17" s="37"/>
+    </row>
+    <row r="18" spans="1:26" ht="25.5">
+      <c r="A18" s="15">
+        <v>46153</v>
+      </c>
+      <c r="B18" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="50"/>
-      <c r="F18" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="37"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="36">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="27"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1786,34 +1920,34 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="49"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="49"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21">
-        <v>46154.0</v>
-      </c>
-      <c r="B19" s="45" t="s">
+      <c r="T18" s="37"/>
+      <c r="U18" s="37"/>
+      <c r="V18" s="37"/>
+      <c r="W18" s="37"/>
+      <c r="X18" s="37"/>
+      <c r="Y18" s="37"/>
+      <c r="Z18" s="37"/>
+    </row>
+    <row r="19" spans="1:26" ht="25.5">
+      <c r="A19" s="15">
+        <v>46154</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="37"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="36">
+        <v>0</v>
+      </c>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="27"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1824,33 +1958,33 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="49"/>
-      <c r="W19" s="49"/>
-      <c r="X19" s="49"/>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="49"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="21">
-        <v>46155.0</v>
-      </c>
-      <c r="B20" s="45" t="s">
+      <c r="T19" s="37"/>
+      <c r="U19" s="37"/>
+      <c r="V19" s="37"/>
+      <c r="W19" s="37"/>
+      <c r="X19" s="37"/>
+      <c r="Y19" s="37"/>
+      <c r="Z19" s="37"/>
+    </row>
+    <row r="20" spans="1:26" ht="25.5">
+      <c r="A20" s="15">
+        <v>46155</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="36">
+        <v>0</v>
+      </c>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1870,25 +2004,25 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21">
-      <c r="A21" s="21">
-        <v>46156.0</v>
-      </c>
-      <c r="B21" s="45" t="s">
+    <row r="21" spans="1:26" ht="25.5">
+      <c r="A21" s="15">
+        <v>46156</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="50"/>
-      <c r="F21" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="36">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1908,25 +2042,25 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22">
-      <c r="A22" s="21">
-        <v>46157.0</v>
-      </c>
-      <c r="B22" s="45" t="s">
+    <row r="22" spans="1:26" ht="38.25">
+      <c r="A22" s="15">
+        <v>46157</v>
+      </c>
+      <c r="B22" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="50"/>
-      <c r="F22" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="36">
+        <v>0</v>
+      </c>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1946,25 +2080,25 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23">
-      <c r="A23" s="21">
-        <v>46158.0</v>
-      </c>
-      <c r="B23" s="45" t="s">
+    <row r="23" spans="1:26" ht="38.25">
+      <c r="A23" s="15">
+        <v>46158</v>
+      </c>
+      <c r="B23" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="50"/>
-      <c r="F23" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36">
+        <v>0</v>
+      </c>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1984,23 +2118,23 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24">
-      <c r="A24" s="21"/>
-      <c r="B24" s="45" t="s">
+    <row r="24" spans="1:26" ht="25.5">
+      <c r="A24" s="15"/>
+      <c r="B24" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="50" t="s">
+      <c r="E24" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="51"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2020,23 +2154,23 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25">
-      <c r="A25" s="21"/>
-      <c r="B25" s="45" t="s">
+    <row r="25" spans="1:26" ht="25.5">
+      <c r="A25" s="15"/>
+      <c r="B25" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="47" t="s">
+      <c r="D25" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="50" t="s">
+      <c r="E25" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="51"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -2056,23 +2190,23 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26">
-      <c r="A26" s="21"/>
-      <c r="B26" s="45" t="s">
+    <row r="26" spans="1:26">
+      <c r="A26" s="15"/>
+      <c r="B26" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="51"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -2092,23 +2226,23 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27">
-      <c r="A27" s="21"/>
-      <c r="B27" s="45" t="s">
+    <row r="27" spans="1:26">
+      <c r="A27" s="15"/>
+      <c r="B27" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="51"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2128,7 +2262,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2156,7 +2290,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2184,7 +2318,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2212,7 +2346,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2240,7 +2374,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2268,7 +2402,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2296,7 +2430,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2324,7 +2458,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2352,7 +2486,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2380,7 +2514,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2408,7 +2542,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2436,7 +2570,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2464,7 +2598,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:26">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2492,7 +2626,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:26">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2520,7 +2654,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2548,7 +2682,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:26">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2576,7 +2710,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2604,7 +2738,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:26">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2632,7 +2766,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:26">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2660,7 +2794,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:26">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2688,7 +2822,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:26">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2716,7 +2850,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:26">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2744,7 +2878,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:26">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2772,7 +2906,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:26">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2800,7 +2934,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:26">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2828,7 +2962,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:26">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2856,7 +2990,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:26">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2884,7 +3018,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:26">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2912,7 +3046,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:26">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2940,7 +3074,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:26">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2968,7 +3102,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:26">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2996,7 +3130,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:26">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3024,7 +3158,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:26">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3052,7 +3186,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:26">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3080,7 +3214,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:26">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3108,7 +3242,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:26">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3136,7 +3270,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:26">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3164,7 +3298,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:26">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3192,7 +3326,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:26">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3220,7 +3354,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:26">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3248,7 +3382,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:26">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3276,7 +3410,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:26">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3304,7 +3438,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:26">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3332,7 +3466,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:26">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3360,7 +3494,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:26">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3388,7 +3522,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:26">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3416,7 +3550,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:26">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3444,7 +3578,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:26">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3472,7 +3606,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:26">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3500,7 +3634,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:26">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3528,7 +3662,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:26">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3556,7 +3690,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:26">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3584,7 +3718,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:26">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3612,7 +3746,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:26">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3640,7 +3774,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:26">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3668,7 +3802,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:26">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3696,7 +3830,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:26">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3724,7 +3858,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:26">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3752,7 +3886,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:26">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3780,7 +3914,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:26">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3808,7 +3942,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:26">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3836,7 +3970,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:26">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3864,7 +3998,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:26">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3892,7 +4026,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:26">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3920,7 +4054,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:26">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3948,7 +4082,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:26">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3976,7 +4110,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:26">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4004,7 +4138,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:26">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4032,7 +4166,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:26">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4060,7 +4194,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:26">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4088,7 +4222,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:26">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4116,7 +4250,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:26">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4144,7 +4278,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:26">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4172,7 +4306,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:26">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4200,7 +4334,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:26">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4228,7 +4362,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:26">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4256,7 +4390,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:26">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4284,7 +4418,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:26">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4312,7 +4446,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:26">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4340,7 +4474,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:26">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4368,7 +4502,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:26">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4396,7 +4530,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:26">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4424,7 +4558,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:26">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4452,7 +4586,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:26">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4480,7 +4614,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:26">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4508,7 +4642,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:26">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4536,7 +4670,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:26">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4564,7 +4698,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:26">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4592,7 +4726,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:26">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4620,7 +4754,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:26">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4648,7 +4782,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:26">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4676,7 +4810,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:26">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4704,7 +4838,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:26">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4732,7 +4866,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:26">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4760,7 +4894,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:26">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4788,7 +4922,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:26">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4816,7 +4950,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:26">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4844,7 +4978,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:26">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4872,7 +5006,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:26">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4900,7 +5034,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:26">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4928,7 +5062,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:26">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4956,7 +5090,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:26">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4984,7 +5118,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:26">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5012,7 +5146,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:26">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5040,7 +5174,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:26">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5068,7 +5202,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:26">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5096,7 +5230,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:26">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5124,7 +5258,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:26">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5152,7 +5286,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:26">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5180,7 +5314,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:26">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5208,7 +5342,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:26">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5236,7 +5370,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:26">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5264,7 +5398,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:26">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5292,7 +5426,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:26">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5320,7 +5454,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:26">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5348,7 +5482,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:26">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5376,7 +5510,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:26">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5404,7 +5538,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:26">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5432,7 +5566,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:26">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5460,7 +5594,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:26">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5488,7 +5622,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:26">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5516,7 +5650,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:26">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5544,7 +5678,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:26">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5572,7 +5706,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:26">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5600,7 +5734,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:26">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5628,7 +5762,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:26">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5656,7 +5790,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:26">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5684,7 +5818,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:26">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5712,7 +5846,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:26">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5740,7 +5874,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:26">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5768,7 +5902,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:26">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5796,7 +5930,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:26">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5824,7 +5958,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:26">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5852,7 +5986,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:26">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5880,7 +6014,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:26">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5908,7 +6042,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:26">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5936,7 +6070,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:26">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5964,7 +6098,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:26">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5992,7 +6126,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:26">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6020,7 +6154,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:26">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6048,7 +6182,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:26">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6076,7 +6210,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:26">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6104,7 +6238,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:26">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6132,7 +6266,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:26">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6160,7 +6294,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:26">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6188,7 +6322,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:26">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6216,7 +6350,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:26">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6244,7 +6378,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:26">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6272,7 +6406,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:26">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6300,7 +6434,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:26">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6328,7 +6462,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:26">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6356,7 +6490,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:26">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6384,7 +6518,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:26">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6412,7 +6546,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:26">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6440,7 +6574,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:26">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6468,7 +6602,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:26">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6496,7 +6630,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:26">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6524,7 +6658,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:26">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6552,7 +6686,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:26">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6580,7 +6714,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:26">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6608,7 +6742,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:26">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6636,7 +6770,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:26">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6664,7 +6798,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:26">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6692,7 +6826,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:26">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6720,7 +6854,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:26">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6748,7 +6882,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:26">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6776,7 +6910,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:26">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6804,7 +6938,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:26">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6832,7 +6966,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:26">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6860,7 +6994,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:26">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6888,7 +7022,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:26">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6916,7 +7050,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:26">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6944,7 +7078,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:26">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6972,7 +7106,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:26">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7000,7 +7134,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:26">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7028,7 +7162,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:26">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7056,7 +7190,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:26">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7084,7 +7218,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:26">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7112,7 +7246,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:26">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7140,7 +7274,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:26">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7168,7 +7302,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:26">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7196,7 +7330,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:26">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7224,7 +7358,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:26">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7252,7 +7386,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:26">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7280,7 +7414,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:26">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7308,7 +7442,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:26">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7336,7 +7470,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:26">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7364,7 +7498,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:26">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7392,7 +7526,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:26">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7420,7 +7554,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:26">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7448,7 +7582,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:26">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7476,7 +7610,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:26">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7504,7 +7638,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:26">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7538,33 +7672,29 @@
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z220"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.86"/>
-    <col customWidth="1" min="2" max="2" width="9.86"/>
-    <col customWidth="1" min="3" max="3" width="27.57"/>
-    <col customWidth="1" min="4" max="4" width="16.14"/>
-    <col customWidth="1" min="5" max="5" width="39.86"/>
-    <col customWidth="1" min="6" max="6" width="28.29"/>
-    <col customWidth="1" min="7" max="7" width="43.71"/>
-    <col customWidth="1" min="8" max="8" width="42.43"/>
-    <col customWidth="1" min="9" max="26" width="10.71"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="39.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" customWidth="1"/>
+    <col min="7" max="7" width="43.7109375" customWidth="1"/>
+    <col min="8" max="8" width="42.42578125" customWidth="1"/>
+    <col min="9" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7592,7 +7722,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -7622,16 +7752,16 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -7654,14 +7784,14 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="1:26" ht="15" customHeight="1">
+      <c r="A4" s="6"/>
+      <c r="B4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -7684,14 +7814,14 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:26" ht="15" customHeight="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -7714,29 +7844,29 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:26" ht="31.5">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="11" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="1"/>
@@ -7758,29 +7888,29 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:26" ht="25.5">
+      <c r="A7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="14" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="1"/>
@@ -7802,29 +7932,29 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="21">
-        <v>46143.0</v>
-      </c>
-      <c r="B8" s="22" t="s">
+    <row r="8" spans="1:26" ht="38.25">
+      <c r="A8" s="15">
+        <v>46143</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="19">
         <v>0.95</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="18" t="s">
         <v>26</v>
       </c>
       <c r="I8" s="1"/>
@@ -7838,33 +7968,33 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21">
-        <v>46144.0</v>
-      </c>
-      <c r="B9" s="22" t="s">
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+    </row>
+    <row r="9" spans="1:26" ht="25.5">
+      <c r="A9" s="15">
+        <v>46144</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="19">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -7876,37 +8006,37 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="21">
-        <v>46145.0</v>
-      </c>
-      <c r="B10" s="30" t="s">
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+    </row>
+    <row r="10" spans="1:26" ht="38.25">
+      <c r="A10" s="15">
+        <v>46145</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="25">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="26"/>
+      <c r="F10" s="19">
+        <v>1</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="18"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -7918,37 +8048,37 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="21">
-        <v>46146.0</v>
-      </c>
-      <c r="B11" s="30" t="s">
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+    </row>
+    <row r="11" spans="1:26" ht="38.25">
+      <c r="A11" s="15">
+        <v>46146</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="19">
         <v>0.2</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="26"/>
+      <c r="H11" s="18"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -7960,36 +8090,40 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="27"/>
-      <c r="Y11" s="27"/>
-      <c r="Z11" s="27"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="21">
-        <v>46147.0</v>
-      </c>
-      <c r="B12" s="32" t="s">
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+    </row>
+    <row r="12" spans="1:26" ht="27" customHeight="1">
+      <c r="A12" s="15">
+        <v>46147</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="37"/>
+      <c r="E12" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="26">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="27"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -8000,34 +8134,34 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21">
-        <v>46148.0</v>
-      </c>
-      <c r="B13" s="32" t="s">
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="15">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="37"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="26">
+        <v>0</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="27"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -8038,36 +8172,36 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="21">
-        <v>46149.0</v>
-      </c>
-      <c r="B14" s="32" t="s">
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="28"/>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" s="15">
+        <v>46149</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="26">
         <v>0.1</v>
       </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="37"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="27"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -8078,80 +8212,80 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="38"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21">
-        <v>46152.0</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="28"/>
+    </row>
+    <row r="15" spans="1:26" ht="76.5">
+      <c r="A15" s="15">
+        <v>46152</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="34" t="s">
+      <c r="E15" s="30"/>
+      <c r="F15" s="26">
+        <v>1</v>
+      </c>
+      <c r="G15" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="34"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="44"/>
-      <c r="V15" s="44"/>
-      <c r="W15" s="44"/>
-      <c r="X15" s="44"/>
-      <c r="Y15" s="44"/>
-      <c r="Z15" s="44"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="21">
-        <v>46152.0</v>
-      </c>
-      <c r="B16" s="45" t="s">
+      <c r="H15" s="25"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+    </row>
+    <row r="16" spans="1:26" ht="153">
+      <c r="A16" s="15">
+        <v>46152</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="E16" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="36">
         <v>0.95</v>
       </c>
-      <c r="G16" s="47" t="s">
+      <c r="G16" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="H16" s="47" t="s">
+      <c r="H16" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="I16" s="37"/>
+      <c r="I16" s="27"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -8162,38 +8296,38 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="49"/>
-      <c r="U16" s="49"/>
-      <c r="V16" s="49"/>
-      <c r="W16" s="49"/>
-      <c r="X16" s="49"/>
-      <c r="Y16" s="49"/>
-      <c r="Z16" s="49"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21">
-        <v>46152.0</v>
-      </c>
-      <c r="B17" s="45" t="s">
+      <c r="T16" s="37"/>
+      <c r="U16" s="37"/>
+      <c r="V16" s="37"/>
+      <c r="W16" s="37"/>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="37"/>
+      <c r="Z16" s="37"/>
+    </row>
+    <row r="17" spans="1:26" ht="76.5">
+      <c r="A17" s="15">
+        <v>46152</v>
+      </c>
+      <c r="B17" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="G17" s="47" t="s">
+      <c r="F17" s="36">
+        <v>1</v>
+      </c>
+      <c r="G17" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="37"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="27"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -8204,34 +8338,34 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="49"/>
-      <c r="W17" s="49"/>
-      <c r="X17" s="49"/>
-      <c r="Y17" s="49"/>
-      <c r="Z17" s="49"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="21">
-        <v>46153.0</v>
-      </c>
-      <c r="B18" s="45" t="s">
+      <c r="T17" s="37"/>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="37"/>
+      <c r="X17" s="37"/>
+      <c r="Y17" s="37"/>
+      <c r="Z17" s="37"/>
+    </row>
+    <row r="18" spans="1:26" ht="25.5">
+      <c r="A18" s="15">
+        <v>46153</v>
+      </c>
+      <c r="B18" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="50"/>
-      <c r="F18" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="37"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="36">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="27"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -8242,34 +8376,40 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="49"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="49"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21">
-        <v>46154.0</v>
-      </c>
-      <c r="B19" s="45" t="s">
+      <c r="T18" s="37"/>
+      <c r="U18" s="37"/>
+      <c r="V18" s="37"/>
+      <c r="W18" s="37"/>
+      <c r="X18" s="37"/>
+      <c r="Y18" s="37"/>
+      <c r="Z18" s="37"/>
+    </row>
+    <row r="19" spans="1:26" ht="27" customHeight="1">
+      <c r="A19" s="15">
+        <v>46154</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="37"/>
+      <c r="E19" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="36">
+        <v>0.8</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="27"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -8280,33 +8420,33 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="49"/>
-      <c r="W19" s="49"/>
-      <c r="X19" s="49"/>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="49"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="21">
-        <v>46155.0</v>
-      </c>
-      <c r="B20" s="45" t="s">
+      <c r="T19" s="37"/>
+      <c r="U19" s="37"/>
+      <c r="V19" s="37"/>
+      <c r="W19" s="37"/>
+      <c r="X19" s="37"/>
+      <c r="Y19" s="37"/>
+      <c r="Z19" s="37"/>
+    </row>
+    <row r="20" spans="1:26" ht="25.5">
+      <c r="A20" s="15">
+        <v>46155</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="36">
+        <v>0</v>
+      </c>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -8326,25 +8466,29 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21">
-      <c r="A21" s="21">
-        <v>46156.0</v>
-      </c>
-      <c r="B21" s="45" t="s">
+    <row r="21" spans="1:26" ht="27.75" customHeight="1">
+      <c r="A21" s="15">
+        <v>46156</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="50"/>
-      <c r="F21" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
+      <c r="E21" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="36">
+        <v>1</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="35"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -8364,25 +8508,25 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22">
-      <c r="A22" s="21">
-        <v>46157.0</v>
-      </c>
-      <c r="B22" s="45" t="s">
+    <row r="22" spans="1:26" ht="38.25">
+      <c r="A22" s="15">
+        <v>46157</v>
+      </c>
+      <c r="B22" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="50"/>
-      <c r="F22" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="36">
+        <v>0</v>
+      </c>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -8402,25 +8546,25 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23">
-      <c r="A23" s="21">
-        <v>46158.0</v>
-      </c>
-      <c r="B23" s="45" t="s">
+    <row r="23" spans="1:26" ht="38.25">
+      <c r="A23" s="15">
+        <v>46158</v>
+      </c>
+      <c r="B23" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="50"/>
-      <c r="F23" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36">
+        <v>0</v>
+      </c>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -8440,23 +8584,23 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24">
-      <c r="A24" s="21"/>
-      <c r="B24" s="45" t="s">
+    <row r="24" spans="1:26" ht="25.5">
+      <c r="A24" s="15"/>
+      <c r="B24" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="50" t="s">
+      <c r="E24" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="51"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -8476,23 +8620,23 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25">
-      <c r="A25" s="21"/>
-      <c r="B25" s="45" t="s">
+    <row r="25" spans="1:26" ht="25.5">
+      <c r="A25" s="15"/>
+      <c r="B25" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="47" t="s">
+      <c r="D25" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="50" t="s">
+      <c r="E25" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="51"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -8512,29 +8656,29 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26">
-      <c r="A26" s="21">
-        <v>46300.0</v>
-      </c>
-      <c r="B26" s="45" t="s">
+    <row r="26" spans="1:26" ht="127.5">
+      <c r="A26" s="15">
+        <v>46300</v>
+      </c>
+      <c r="B26" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="G26" s="47" t="s">
+      <c r="F26" s="36">
+        <v>1</v>
+      </c>
+      <c r="G26" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="50"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -8554,29 +8698,29 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27">
-      <c r="A27" s="21">
-        <v>46300.0</v>
-      </c>
-      <c r="B27" s="45" t="s">
+    <row r="27" spans="1:26" ht="51">
+      <c r="A27" s="15">
+        <v>46300</v>
+      </c>
+      <c r="B27" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="G27" s="47" t="s">
+      <c r="F27" s="36">
+        <v>1</v>
+      </c>
+      <c r="G27" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="H27" s="50"/>
+      <c r="H27" s="35"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -8596,7 +8740,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -8624,7 +8768,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -8652,7 +8796,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -8680,7 +8824,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -8708,7 +8852,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -8736,7 +8880,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -8764,7 +8908,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -8792,7 +8936,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -8820,7 +8964,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -8848,7 +8992,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -8876,7 +9020,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -8904,7 +9048,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -8932,7 +9076,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:26">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -8960,7 +9104,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:26">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -8988,7 +9132,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -9016,7 +9160,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:26">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -9044,7 +9188,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -9072,7 +9216,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:26">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -9100,7 +9244,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:26">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -9128,7 +9272,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:26">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -9156,7 +9300,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:26">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -9184,7 +9328,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:26">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -9212,7 +9356,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:26">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -9240,7 +9384,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:26">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -9268,7 +9412,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:26">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -9296,7 +9440,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:26">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -9324,7 +9468,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:26">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -9352,7 +9496,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:26">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -9380,7 +9524,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:26">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -9408,7 +9552,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:26">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -9436,7 +9580,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:26">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -9464,7 +9608,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:26">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -9492,7 +9636,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:26">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -9520,7 +9664,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:26">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -9548,7 +9692,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:26">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -9576,7 +9720,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:26">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -9604,7 +9748,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:26">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -9632,7 +9776,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:26">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -9660,7 +9804,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:26">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -9688,7 +9832,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:26">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -9716,7 +9860,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:26">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -9744,7 +9888,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:26">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -9772,7 +9916,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:26">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -9800,7 +9944,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:26">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -9828,7 +9972,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:26">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -9856,7 +10000,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:26">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -9884,7 +10028,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:26">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -9912,7 +10056,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:26">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -9940,7 +10084,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:26">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -9968,7 +10112,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:26">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -9996,7 +10140,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:26">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -10024,7 +10168,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:26">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -10052,7 +10196,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:26">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -10080,7 +10224,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:26">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -10108,7 +10252,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:26">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -10136,7 +10280,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:26">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -10164,7 +10308,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:26">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -10192,7 +10336,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:26">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -10220,7 +10364,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:26">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -10248,7 +10392,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:26">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -10276,7 +10420,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:26">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -10304,7 +10448,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:26">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -10332,7 +10476,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:26">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -10360,7 +10504,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:26">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -10388,7 +10532,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:26">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -10416,7 +10560,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:26">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -10444,7 +10588,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:26">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -10472,7 +10616,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:26">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -10500,7 +10644,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:26">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -10528,7 +10672,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:26">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -10556,7 +10700,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:26">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -10584,7 +10728,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:26">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -10612,7 +10756,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:26">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -10640,7 +10784,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:26">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -10668,7 +10812,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:26">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -10696,7 +10840,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:26">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -10724,7 +10868,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:26">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -10752,7 +10896,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:26">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -10780,7 +10924,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:26">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -10808,7 +10952,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:26">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -10836,7 +10980,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:26">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -10864,7 +11008,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:26">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -10892,7 +11036,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:26">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -10920,7 +11064,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:26">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -10948,7 +11092,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:26">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -10976,7 +11120,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:26">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -11004,7 +11148,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:26">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -11032,7 +11176,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:26">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -11060,7 +11204,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:26">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -11088,7 +11232,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:26">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -11116,7 +11260,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:26">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -11144,7 +11288,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:26">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -11172,7 +11316,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:26">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -11200,7 +11344,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:26">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -11228,7 +11372,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:26">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -11256,7 +11400,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:26">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -11284,7 +11428,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:26">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -11312,7 +11456,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:26">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -11340,7 +11484,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:26">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -11368,7 +11512,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:26">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -11396,7 +11540,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:26">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -11424,7 +11568,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:26">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -11452,7 +11596,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:26">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -11480,7 +11624,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:26">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -11508,7 +11652,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:26">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -11536,7 +11680,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:26">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -11564,7 +11708,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:26">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -11592,7 +11736,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:26">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -11620,7 +11764,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:26">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -11648,7 +11792,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:26">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -11676,7 +11820,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:26">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -11704,7 +11848,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:26">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -11732,7 +11876,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:26">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -11760,7 +11904,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:26">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -11788,7 +11932,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:26">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -11816,7 +11960,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:26">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -11844,7 +11988,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:26">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -11872,7 +12016,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:26">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -11900,7 +12044,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:26">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -11928,7 +12072,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:26">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -11956,7 +12100,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:26">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -11984,7 +12128,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:26">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -12012,7 +12156,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:26">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -12040,7 +12184,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:26">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -12068,7 +12212,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:26">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -12096,7 +12240,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:26">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -12124,7 +12268,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:26">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -12152,7 +12296,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:26">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -12180,7 +12324,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:26">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -12208,7 +12352,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:26">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -12236,7 +12380,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:26">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -12264,7 +12408,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:26">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -12292,7 +12436,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:26">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -12320,7 +12464,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:26">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -12348,7 +12492,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:26">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -12376,7 +12520,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:26">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -12404,7 +12548,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:26">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -12432,7 +12576,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:26">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -12460,7 +12604,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:26">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -12488,7 +12632,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:26">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -12516,7 +12660,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:26">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -12544,7 +12688,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:26">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -12572,7 +12716,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:26">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -12600,7 +12744,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:26">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -12628,7 +12772,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:26">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -12656,7 +12800,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:26">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -12684,7 +12828,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:26">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -12712,7 +12856,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:26">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -12740,7 +12884,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:26">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -12768,7 +12912,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:26">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -12796,7 +12940,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:26">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -12824,7 +12968,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:26">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -12852,7 +12996,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:26">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -12880,7 +13024,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:26">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -12908,7 +13052,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:26">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -12936,7 +13080,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:26">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -12964,7 +13108,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:26">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -12992,7 +13136,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:26">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -13020,7 +13164,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:26">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -13048,7 +13192,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:26">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -13076,7 +13220,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:26">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -13104,7 +13248,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:26">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -13132,7 +13276,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:26">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -13160,7 +13304,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:26">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -13188,7 +13332,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:26">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -13216,7 +13360,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:26">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -13244,7 +13388,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:26">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -13272,7 +13416,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:26">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -13300,7 +13444,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:26">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -13328,7 +13472,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:26">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -13356,7 +13500,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:26">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -13384,7 +13528,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:26">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -13412,7 +13556,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:26">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -13440,7 +13584,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:26">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -13468,7 +13612,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:26">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -13496,7 +13640,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:26">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -13524,7 +13668,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:26">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -13552,7 +13696,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:26">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -13580,7 +13724,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:26">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -13608,7 +13752,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:26">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -13636,7 +13780,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:26">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -13664,7 +13808,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:26">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -13692,7 +13836,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:26">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -13720,7 +13864,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:26">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -13748,7 +13892,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:26">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -13776,7 +13920,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:26">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -13804,7 +13948,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:26">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -13832,7 +13976,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:26">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -13860,7 +14004,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:26">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -13888,7 +14032,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:26">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -13916,7 +14060,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:26">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -13944,7 +14088,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:26">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -13972,7 +14116,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:26">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -14006,30 +14150,29 @@
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:H1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.29"/>
-    <col customWidth="1" min="2" max="2" width="10.14"/>
-    <col customWidth="1" min="3" max="3" width="27.14"/>
-    <col customWidth="1" min="4" max="4" width="13.86"/>
-    <col customWidth="1" min="5" max="6" width="14.43"/>
-    <col customWidth="1" min="7" max="7" width="39.14"/>
-    <col customWidth="1" min="8" max="8" width="72.29"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="39.140625" customWidth="1"/>
+    <col min="8" max="8" width="72.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14039,7 +14182,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" ht="21">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -14051,447 +14194,447 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" ht="21">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="1:8" ht="21">
+      <c r="A4" s="6"/>
+      <c r="B4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:8" ht="21">
+      <c r="A5" s="6"/>
+      <c r="B5" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:8" ht="31.5">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:8" ht="25.5">
+      <c r="A7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="27.75" customHeight="1">
-      <c r="A8" s="21">
-        <v>46143.0</v>
-      </c>
-      <c r="B8" s="22" t="s">
+    <row r="8" spans="1:8" ht="27.75" customHeight="1">
+      <c r="A8" s="15">
+        <v>46143</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="19">
         <v>0.9</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" ht="34.5" customHeight="1">
-      <c r="A9" s="21">
-        <v>46144.0</v>
-      </c>
-      <c r="B9" s="22" t="s">
+    <row r="9" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A9" s="15">
+        <v>46144</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-    </row>
-    <row r="10" ht="33.0" customHeight="1">
-      <c r="A10" s="21">
-        <v>46145.0</v>
-      </c>
-      <c r="B10" s="30" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="19">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:8" ht="33" customHeight="1">
+      <c r="A10" s="15">
+        <v>46145</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="19">
         <v>0.2</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="26"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="21">
-        <v>46146.0</v>
-      </c>
-      <c r="B11" s="30" t="s">
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:8" ht="38.25">
+      <c r="A11" s="15">
+        <v>46146</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="19">
         <v>0.2</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="26"/>
-    </row>
-    <row r="12" ht="37.5" customHeight="1">
-      <c r="A12" s="21">
-        <v>46147.0</v>
-      </c>
-      <c r="B12" s="32" t="s">
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:8" ht="37.5" customHeight="1">
+      <c r="A12" s="15">
+        <v>46147</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="35" t="s">
+      <c r="E12" s="25"/>
+      <c r="F12" s="26">
+        <v>0</v>
+      </c>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" ht="36.0" customHeight="1">
-      <c r="A13" s="21">
-        <v>46148.0</v>
-      </c>
-      <c r="B13" s="32" t="s">
+    <row r="13" spans="1:8" ht="36" customHeight="1">
+      <c r="A13" s="15">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-    </row>
-    <row r="14" ht="33.75" customHeight="1">
-      <c r="A14" s="21">
-        <v>46149.0</v>
-      </c>
-      <c r="B14" s="32" t="s">
+      <c r="E13" s="25"/>
+      <c r="F13" s="26">
+        <v>0</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+    </row>
+    <row r="14" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A14" s="15">
+        <v>46149</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="26">
         <v>0.1</v>
       </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-    </row>
-    <row r="15" ht="34.5" customHeight="1">
-      <c r="A15" s="21">
-        <v>46150.0</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+    </row>
+    <row r="15" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A15" s="15">
+        <v>46150</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="35" t="s">
+      <c r="E15" s="30"/>
+      <c r="F15" s="26">
+        <v>0</v>
+      </c>
+      <c r="G15" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="35" t="s">
+      <c r="H15" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" ht="40.5" customHeight="1">
-      <c r="A16" s="21">
-        <v>46151.0</v>
-      </c>
-      <c r="B16" s="45" t="s">
+    <row r="16" spans="1:8" ht="40.5" customHeight="1">
+      <c r="A16" s="15">
+        <v>46151</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-    </row>
-    <row r="17" ht="33.0" customHeight="1">
-      <c r="A17" s="21">
-        <v>46152.0</v>
-      </c>
-      <c r="B17" s="45" t="s">
+      <c r="E16" s="35"/>
+      <c r="F16" s="36">
+        <v>0</v>
+      </c>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+    </row>
+    <row r="17" spans="1:8" ht="33" customHeight="1">
+      <c r="A17" s="15">
+        <v>46152</v>
+      </c>
+      <c r="B17" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-    </row>
-    <row r="18" ht="39.0" customHeight="1">
-      <c r="A18" s="21">
-        <v>46153.0</v>
-      </c>
-      <c r="B18" s="45" t="s">
+      <c r="E17" s="35"/>
+      <c r="F17" s="36">
+        <v>0</v>
+      </c>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+    </row>
+    <row r="18" spans="1:8" ht="39" customHeight="1">
+      <c r="A18" s="15">
+        <v>46153</v>
+      </c>
+      <c r="B18" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="50"/>
-      <c r="F18" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21">
-        <v>46154.0</v>
-      </c>
-      <c r="B19" s="45" t="s">
+      <c r="E18" s="35"/>
+      <c r="F18" s="36">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+    </row>
+    <row r="19" spans="1:8" ht="25.5">
+      <c r="A19" s="15">
+        <v>46154</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="21">
-        <v>46155.0</v>
-      </c>
-      <c r="B20" s="45" t="s">
+      <c r="E19" s="35"/>
+      <c r="F19" s="36">
+        <v>0</v>
+      </c>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+    </row>
+    <row r="20" spans="1:8" ht="25.5">
+      <c r="A20" s="15">
+        <v>46155</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="21">
-        <v>46156.0</v>
-      </c>
-      <c r="B21" s="45" t="s">
+      <c r="E20" s="35"/>
+      <c r="F20" s="36">
+        <v>0</v>
+      </c>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A21" s="15">
+        <v>46156</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="50"/>
-      <c r="F21" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="21">
-        <v>46157.0</v>
-      </c>
-      <c r="B22" s="45" t="s">
+      <c r="E21" s="35"/>
+      <c r="F21" s="36">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A22" s="15">
+        <v>46157</v>
+      </c>
+      <c r="B22" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="50"/>
-      <c r="F22" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="21">
-        <v>46158.0</v>
-      </c>
-      <c r="B23" s="45" t="s">
+      <c r="E22" s="35"/>
+      <c r="F22" s="36">
+        <v>0</v>
+      </c>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A23" s="15">
+        <v>46158</v>
+      </c>
+      <c r="B23" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="50"/>
-      <c r="F23" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36">
+        <v>0</v>
+      </c>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -15466,28 +15609,29 @@
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
   </mergeCells>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:H1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.0"/>
-    <col customWidth="1" min="2" max="2" width="10.14"/>
-    <col customWidth="1" min="3" max="3" width="27.14"/>
-    <col customWidth="1" min="4" max="4" width="13.86"/>
-    <col customWidth="1" min="5" max="6" width="14.43"/>
-    <col customWidth="1" min="7" max="7" width="22.43"/>
-    <col customWidth="1" min="8" max="8" width="14.14"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15497,7 +15641,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" ht="21">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -15509,447 +15653,447 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" ht="21">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="1:8" ht="21">
+      <c r="A4" s="6"/>
+      <c r="B4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:8" ht="21">
+      <c r="A5" s="6"/>
+      <c r="B5" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:8" ht="51">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="27.75" customHeight="1">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:8" ht="27.75" customHeight="1">
+      <c r="A7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="34.5" customHeight="1">
-      <c r="A8" s="21">
-        <v>46143.0</v>
-      </c>
-      <c r="B8" s="22" t="s">
+    <row r="8" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A8" s="15">
+        <v>46143</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="19">
         <v>0.9</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" ht="33.0" customHeight="1">
-      <c r="A9" s="21">
-        <v>46144.0</v>
-      </c>
-      <c r="B9" s="22" t="s">
+    <row r="9" spans="1:8" ht="33" customHeight="1">
+      <c r="A9" s="15">
+        <v>46144</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="21">
-        <v>46145.0</v>
-      </c>
-      <c r="B10" s="30" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="19">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:8" ht="38.25">
+      <c r="A10" s="15">
+        <v>46145</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="19">
         <v>0.2</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="26"/>
-    </row>
-    <row r="11" ht="37.5" customHeight="1">
-      <c r="A11" s="21">
-        <v>46146.0</v>
-      </c>
-      <c r="B11" s="30" t="s">
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:8" ht="37.5" customHeight="1">
+      <c r="A11" s="15">
+        <v>46146</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="19">
         <v>0.2</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="26"/>
-    </row>
-    <row r="12" ht="36.0" customHeight="1">
-      <c r="A12" s="21">
-        <v>46147.0</v>
-      </c>
-      <c r="B12" s="32" t="s">
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:8" ht="36" customHeight="1">
+      <c r="A12" s="15">
+        <v>46147</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="35" t="s">
+      <c r="E12" s="25"/>
+      <c r="F12" s="26">
+        <v>0</v>
+      </c>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" ht="33.75" customHeight="1">
-      <c r="A13" s="21">
-        <v>46148.0</v>
-      </c>
-      <c r="B13" s="32" t="s">
+    <row r="13" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A13" s="15">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-    </row>
-    <row r="14" ht="34.5" customHeight="1">
-      <c r="A14" s="21">
-        <v>46149.0</v>
-      </c>
-      <c r="B14" s="32" t="s">
+      <c r="E13" s="25"/>
+      <c r="F13" s="26">
+        <v>0</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+    </row>
+    <row r="14" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A14" s="15">
+        <v>46149</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="26">
         <v>0.1</v>
       </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-    </row>
-    <row r="15" ht="40.5" customHeight="1">
-      <c r="A15" s="21">
-        <v>46150.0</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+    </row>
+    <row r="15" spans="1:8" ht="40.5" customHeight="1">
+      <c r="A15" s="15">
+        <v>46150</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="35" t="s">
+      <c r="E15" s="30"/>
+      <c r="F15" s="26">
+        <v>0</v>
+      </c>
+      <c r="G15" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="35" t="s">
+      <c r="H15" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" ht="33.0" customHeight="1">
-      <c r="A16" s="21">
-        <v>46151.0</v>
-      </c>
-      <c r="B16" s="45" t="s">
+    <row r="16" spans="1:8" ht="33" customHeight="1">
+      <c r="A16" s="15">
+        <v>46151</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-    </row>
-    <row r="17" ht="39.0" customHeight="1">
-      <c r="A17" s="21">
-        <v>46152.0</v>
-      </c>
-      <c r="B17" s="45" t="s">
+      <c r="E16" s="35"/>
+      <c r="F16" s="36">
+        <v>0</v>
+      </c>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+    </row>
+    <row r="17" spans="1:8" ht="39" customHeight="1">
+      <c r="A17" s="15">
+        <v>46152</v>
+      </c>
+      <c r="B17" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-    </row>
-    <row r="18" ht="35.25" customHeight="1">
-      <c r="A18" s="21">
-        <v>46153.0</v>
-      </c>
-      <c r="B18" s="45" t="s">
+      <c r="E17" s="35"/>
+      <c r="F17" s="36">
+        <v>0</v>
+      </c>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+    </row>
+    <row r="18" spans="1:8" ht="35.25" customHeight="1">
+      <c r="A18" s="15">
+        <v>46153</v>
+      </c>
+      <c r="B18" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="50"/>
-      <c r="F18" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21">
-        <v>46154.0</v>
-      </c>
-      <c r="B19" s="45" t="s">
+      <c r="E18" s="35"/>
+      <c r="F18" s="36">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+    </row>
+    <row r="19" spans="1:8" ht="25.5">
+      <c r="A19" s="15">
+        <v>46154</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="21">
-        <v>46155.0</v>
-      </c>
-      <c r="B20" s="45" t="s">
+      <c r="E19" s="35"/>
+      <c r="F19" s="36">
+        <v>0</v>
+      </c>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+    </row>
+    <row r="20" spans="1:8" ht="25.5">
+      <c r="A20" s="15">
+        <v>46155</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="21">
-        <v>46156.0</v>
-      </c>
-      <c r="B21" s="45" t="s">
+      <c r="E20" s="35"/>
+      <c r="F20" s="36">
+        <v>0</v>
+      </c>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A21" s="15">
+        <v>46156</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="50"/>
-      <c r="F21" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="21">
-        <v>46157.0</v>
-      </c>
-      <c r="B22" s="45" t="s">
+      <c r="E21" s="35"/>
+      <c r="F21" s="36">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A22" s="15">
+        <v>46157</v>
+      </c>
+      <c r="B22" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="50"/>
-      <c r="F22" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="21">
-        <v>46158.0</v>
-      </c>
-      <c r="B23" s="45" t="s">
+      <c r="E22" s="35"/>
+      <c r="F22" s="36">
+        <v>0</v>
+      </c>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A23" s="15">
+        <v>46158</v>
+      </c>
+      <c r="B23" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="50"/>
-      <c r="F23" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36">
+        <v>0</v>
+      </c>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -16924,7 +17068,7 @@
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
   </mergeCells>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>